--- a/basedatos_partidas/salida/descompuestos/CT-08-04-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-04-010.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 08 Pisos y pavimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Pisos de madera y laminados</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-08-04-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-04-010.xlsx
@@ -485,7 +485,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colocación de piso laminado flotante sobre manta acústica, montado por encastre sin adhesivo, con junta perimetral de dilatación. El sistema flotante exige que la junta perimetral quede libre en todo el contorno y oculta bajo el rodapié: si el piso queda a tope contra la pared, al dilatar se abomba y levanta. Incluye la comprobación de la planitud y humedad del contrapiso, el extendido de la manta con solapes sellados, el replanteo del sentido de las tablas y del ancho de la última hilera, el montaje por encastre con cuñas perimetrales, los cortes de ajuste en marcos y tuberías y el retiro de las cuñas. El piso lo elige el cliente y se presupuesta aparte. Medido en superficie realmente ejecutada, descontando huecos mayores de 1 m².
+          <t xml:space="preserve">Colocación de piso laminado flotante sobre manta acústica, montado por encastre sin adhesivo, con junta perimetral de dilatación. El sistema flotante exige que la junta perimetral quede libre en todo el contorno y oculta bajo el rodapié: si el piso queda a tope contra la pared, al dilatar se abomba y levanta. Incluye la comprobación de la planitud y humedad del afirmado, el extendido de la manta con solapes sellados, el replanteo del sentido de las tablas y del ancho de la última hilera, el montaje por encastre con cuñas perimetrales, los cortes de ajuste en marcos y tuberías y el retiro de las cuñas. El piso lo elige el cliente y se presupuesta aparte. Medido en superficie realmente ejecutada, descontando huecos mayores de 1 m².
 </t>
         </is>
       </c>
